--- a/data/trans_orig/IP07C16-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C16-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2007 (tasa de respuesta: 89,29%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre en 2007 (tasa de respuesta: 89,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40668</t>
+          <t>39858</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57974</t>
+          <t>57424</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39102</t>
+          <t>38597</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56075</t>
+          <t>57263</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83502</t>
+          <t>84781</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>108760</t>
+          <t>108773</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,88%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36231</t>
+          <t>37160</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53410</t>
+          <t>53157</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49610</t>
+          <t>48577</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67396</t>
+          <t>66780</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>90165</t>
+          <t>89609</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>115169</t>
+          <t>116187</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>50,07%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>9230</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21113</t>
+          <t>20471</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8728</t>
+          <t>8753</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19486</t>
+          <t>19774</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20076</t>
+          <t>20714</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35884</t>
+          <t>35534</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>574</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>7907</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60081</t>
+          <t>59482</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81842</t>
+          <t>80687</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67046</t>
+          <t>66764</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88314</t>
+          <t>89004</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>133820</t>
+          <t>132321</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>162422</t>
+          <t>162970</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,72%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66059</t>
+          <t>65772</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87599</t>
+          <t>86520</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66821</t>
+          <t>66926</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87334</t>
+          <t>87731</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>138458</t>
+          <t>139160</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>167904</t>
+          <t>169443</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,5%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>18078</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33328</t>
+          <t>33618</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19918</t>
+          <t>19825</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35532</t>
+          <t>35693</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>41972</t>
+          <t>42393</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>63771</t>
+          <t>63280</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10993</t>
+          <t>9983</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7930</t>
+          <t>7798</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16271</t>
+          <t>15617</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>107476</t>
+          <t>106768</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133334</t>
+          <t>134817</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>112214</t>
+          <t>111628</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>138585</t>
+          <t>138578</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>227729</t>
+          <t>227110</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>263319</t>
+          <t>265743</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,56%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>107019</t>
+          <t>107171</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>132199</t>
+          <t>134159</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122374</t>
+          <t>122234</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>149263</t>
+          <t>148911</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>238069</t>
+          <t>236164</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>272780</t>
+          <t>277010</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>46,44%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30199</t>
+          <t>30084</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48446</t>
+          <t>48631</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32094</t>
+          <t>31900</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50515</t>
+          <t>51044</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>67207</t>
+          <t>66893</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>93084</t>
+          <t>94589</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13689</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2742</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10481</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>8693</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21307</t>
+          <t>21547</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>683</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2012 (tasa de respuesta: 95,2%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre en 2012 (tasa de respuesta: 95,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62797</t>
+          <t>64739</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83485</t>
+          <t>84383</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60788</t>
+          <t>59478</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81595</t>
+          <t>80238</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>129921</t>
+          <t>129471</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>157313</t>
+          <t>159542</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>52,64%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49945</t>
+          <t>50438</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69582</t>
+          <t>69144</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44226</t>
+          <t>45154</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64097</t>
+          <t>63284</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100237</t>
+          <t>98986</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>126946</t>
+          <t>128315</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9769</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22621</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18973</t>
+          <t>19113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35211</t>
+          <t>34572</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33062</t>
+          <t>32429</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52575</t>
+          <t>53004</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4270</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>625</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61079</t>
+          <t>61028</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82115</t>
+          <t>81845</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>76509</t>
+          <t>76563</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98907</t>
+          <t>98807</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>144210</t>
+          <t>144580</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>174855</t>
+          <t>174274</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,56%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54157</t>
+          <t>52607</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75233</t>
+          <t>72957</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55004</t>
+          <t>55069</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74882</t>
+          <t>76529</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>113720</t>
+          <t>115246</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144036</t>
+          <t>143620</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,31%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14276</t>
+          <t>14468</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27798</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10781</t>
+          <t>10384</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22747</t>
+          <t>23052</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>28780</t>
+          <t>27817</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47508</t>
+          <t>47162</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>8539</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1411</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4607</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>578</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>6820</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>131633</t>
+          <t>130908</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>161209</t>
+          <t>160430</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>145107</t>
+          <t>140888</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>173775</t>
+          <t>171065</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>282303</t>
+          <t>284324</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>322660</t>
+          <t>324255</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>51,09%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>109959</t>
+          <t>109008</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>137522</t>
+          <t>137725</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>105097</t>
+          <t>104619</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>134851</t>
+          <t>134653</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>223408</t>
+          <t>222853</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>262436</t>
+          <t>263010</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28262</t>
+          <t>28458</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46525</t>
+          <t>47279</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32871</t>
+          <t>33550</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52274</t>
+          <t>52875</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>66040</t>
+          <t>65083</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>93579</t>
+          <t>92040</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9456</t>
+          <t>9753</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11626</t>
+          <t>11284</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>9564</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72506</t>
+          <t>73070</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94938</t>
+          <t>94807</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69069</t>
+          <t>67695</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>92014</t>
+          <t>90508</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>148199</t>
+          <t>149168</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>180835</t>
+          <t>181266</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,61%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58517</t>
+          <t>59144</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79950</t>
+          <t>80521</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55703</t>
+          <t>55318</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77801</t>
+          <t>76674</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118358</t>
+          <t>120043</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150937</t>
+          <t>150765</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,09%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16761</t>
+          <t>17250</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32477</t>
+          <t>32448</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20220</t>
+          <t>20895</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36855</t>
+          <t>37237</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41727</t>
+          <t>41625</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63746</t>
+          <t>63733</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>762</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6767</t>
+          <t>6593</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9689</t>
+          <t>9509</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13009</t>
+          <t>12315</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52223</t>
+          <t>52228</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73835</t>
+          <t>73443</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59848</t>
+          <t>59100</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81384</t>
+          <t>81847</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119329</t>
+          <t>118091</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149709</t>
+          <t>149003</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,56%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58614</t>
+          <t>57624</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79645</t>
+          <t>79705</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65162</t>
+          <t>63407</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86556</t>
+          <t>87105</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>127998</t>
+          <t>128545</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>158948</t>
+          <t>158061</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,27%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>19937</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35917</t>
+          <t>36543</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13843</t>
+          <t>13464</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27931</t>
+          <t>27863</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>37218</t>
+          <t>35999</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>59461</t>
+          <t>58324</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9009</t>
+          <t>9325</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7921</t>
+          <t>8008</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14087</t>
+          <t>14015</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -6418,12 +6418,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>613</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>130054</t>
+          <t>132149</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>162465</t>
+          <t>162357</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>135332</t>
+          <t>134576</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>166544</t>
+          <t>165548</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>275300</t>
+          <t>274918</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>318772</t>
+          <t>318754</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>121193</t>
+          <t>122242</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>152834</t>
+          <t>152691</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>124687</t>
+          <t>126125</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>155226</t>
+          <t>156471</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>256512</t>
+          <t>252808</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>300944</t>
+          <t>298504</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,1%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40773</t>
+          <t>41040</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62383</t>
+          <t>62274</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38480</t>
+          <t>37151</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60807</t>
+          <t>58875</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>84450</t>
+          <t>84793</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>114198</t>
+          <t>116119</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12760</t>
+          <t>13233</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14087</t>
+          <t>14831</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>10009</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23195</t>
+          <t>22903</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -7100,12 +7100,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>786</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>6722</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>795</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07C16-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C16-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido estar al aire libre en 2007 (tasa de respuesta: 89,29%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el/la menor en 2007 (tasa de respuesta: 89,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>47546</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>39608</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>56416</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>39,14%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>32,61%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>46,44%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>49101</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>39858</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>57424</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>40589</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>56761</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>44,41%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>36,05%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>51,94%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>47546</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>38597</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>57263</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>39,14%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>84781</t>
+          <t>84826</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>108773</t>
+          <t>108973</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,96%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>57951</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>48602</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>66367</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>47,7%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>40,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>54,63%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>44430</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>37160</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>53157</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>36850</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>52559</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>40,19%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>33,61%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>48,08%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>57951</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>48577</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>66780</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>47,7%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>89609</t>
+          <t>90487</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116187</t>
+          <t>115895</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>49,95%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13440</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8570</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19922</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11,06%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>7,05%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>16,4%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>14161</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9230</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>20471</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>9335</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>20790</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>12,81%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,35%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,52%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>13440</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>8753</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>19774</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>11,06%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20714</t>
+          <t>20323</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35534</t>
+          <t>36067</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -1066,67 +1066,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1856</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5059</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>2130</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>668</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5853</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5780</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,93%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,6%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1856</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>574</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5004</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7907</t>
+          <t>8489</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -1179,102 +1179,102 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3476</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>733</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2982</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4189</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1418</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4321</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4966</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1418</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4328</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>121479</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>121479</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>121479</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>110555</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>110555</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>110555</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>121479</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>121479</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>121479</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>77616</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>67146</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>88090</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>41,71%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>36,08%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>47,34%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>71202</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>59482</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>80687</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>60492</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>82441</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>39,93%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>33,36%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>45,25%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>77616</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>66764</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>89004</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>41,71%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>132321</t>
+          <t>134978</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>162970</t>
+          <t>163758</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,94%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>77462</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>66722</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>88167</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>41,62%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>35,85%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>47,38%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>75584</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>65772</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>86520</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>65076</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>86533</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>42,39%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>36,89%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>48,52%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>77462</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>66926</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>87731</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>41,62%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>139160</t>
+          <t>137560</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>169443</t>
+          <t>167277</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>45,9%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27158</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>20121</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35929</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>14,59%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>10,81%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>19,31%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>25091</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>18078</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>33618</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>18868</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>34364</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>14,07%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>10,14%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>18,85%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>27158</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>19825</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35693</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>14,59%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42393</t>
+          <t>42112</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>63280</t>
+          <t>63096</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3861</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1366</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7936</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5633</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2385</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9983</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2677</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10420</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,16%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,6%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3861</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1352</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7798</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15617</t>
+          <t>15472</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -1856,107 +1856,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>793</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4379</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3619</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,44%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>3973</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>793</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3545</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>186097</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>186097</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>186097</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>263</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>178303</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>178303</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>178303</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>186097</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>186097</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>186097</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>125162</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>111979</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>138981</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>40,69%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>36,41%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>45,19%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>120303</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>106768</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>134817</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>106814</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>133056</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>41,65%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>36,96%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>46,67%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>125162</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>111628</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>138578</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>40,69%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>227110</t>
+          <t>225786</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>265743</t>
+          <t>264113</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,28%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>135413</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>120033</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>150038</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>44,03%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>39,03%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>48,78%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>120014</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>107171</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>134159</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>106118</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>133341</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>41,55%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>37,1%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>46,44%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>135413</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>122234</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>148911</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>44,03%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>236164</t>
+          <t>236249</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>277010</t>
+          <t>275181</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,14%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>40598</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>31717</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>50859</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>13,2%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>10,31%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>16,54%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>39253</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>30084</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>48631</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>30838</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>49762</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>13,59%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>10,41%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>16,84%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>40598</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>31900</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>51044</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>13,2%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>66893</t>
+          <t>67449</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>94589</t>
+          <t>93931</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5717</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2801</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>10808</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>7763</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>4104</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>12905</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>13423</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>2,69%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>1,42%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>5717</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2742</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>10504</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8693</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21547</t>
+          <t>20052</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -2538,92 +2538,92 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3892</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>1526</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5307</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5594</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,53%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2211</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>685</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4194</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>2211</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>307576</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>307576</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>307576</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>429</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>288858</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>288858</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>288858</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>463</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>307576</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>307576</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>307576</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido estar al aire libre en 2012 (tasa de respuesta: 95,2%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el/la menor en 2012 (tasa de respuesta: 95,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>70272</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>61115</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>80616</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>45,89%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>39,91%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>52,64%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>73949</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>64739</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>84383</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>63439</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>83986</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>49,31%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>43,17%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>56,27%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>70272</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>59478</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>80238</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>45,89%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>129471</t>
+          <t>130459</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159542</t>
+          <t>157991</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,12%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>53899</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>43445</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>63391</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>35,2%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>28,37%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>41,39%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>59668</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50438</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>69144</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>49702</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>69616</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>39,79%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>33,63%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>46,11%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>53899</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>45154</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>63284</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>35,2%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98986</t>
+          <t>100881</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>128315</t>
+          <t>127372</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,02%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>26238</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19074</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>34343</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>17,13%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>12,45%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>22,43%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>15505</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>10318</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>22250</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>9788</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>21701</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>10,34%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,88%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>14,84%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>26238</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>19113</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>34572</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>17,13%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32429</t>
+          <t>33317</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53004</t>
+          <t>53633</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4607</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>842</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4477</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3388</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,56%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3979</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>624</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>6468</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -3450,107 +3450,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5046</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>1430</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4450</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>5138</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1430</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4787</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>153143</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>153143</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>153143</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>149965</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>149965</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>149965</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>153143</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>153143</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>153143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>87977</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>77768</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>99310</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>51,55%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>45,57%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>58,19%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>70885</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>61028</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>81845</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>60335</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>81138</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>44,05%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,92%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>50,86%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>87977</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>76563</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>98807</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>51,55%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>144580</t>
+          <t>143086</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>174274</t>
+          <t>175159</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>52,83%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>64856</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>54425</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>75223</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>38,01%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>31,89%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>44,08%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>64171</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>52607</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>72957</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>53305</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>74826</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>39,88%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>32,69%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>45,34%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>64856</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>55069</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>76529</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>38,01%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>115246</t>
+          <t>114939</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143620</t>
+          <t>144516</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,58%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15978</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10461</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>22548</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9,36%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6,13%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>13,21%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>20936</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>14468</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>13873</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>29124</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>13,01%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>8,99%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>18,64%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>15978</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>10384</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>23052</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,36%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27817</t>
+          <t>28299</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47162</t>
+          <t>47493</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>4017</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1853</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8539</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1482</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8442</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,5%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8502</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -4132,72 +4132,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5148</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>916</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4554</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5134</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1840</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4779</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>912</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170651</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170651</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170651</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>160925</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>160925</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>160925</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170651</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170651</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170651</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>158250</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>143652</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>172875</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>48,87%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>44,37%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>53,39%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>144835</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>130908</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>160430</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>130708</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>159989</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>46,59%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>42,11%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>51,6%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>158250</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>140888</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>171065</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>48,87%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>284324</t>
+          <t>283031</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>324255</t>
+          <t>322840</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>50,87%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>118755</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>105356</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>134332</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,68%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>32,54%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>41,49%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>123839</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>109008</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>137725</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>111189</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>138806</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>39,83%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>35,06%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>44,3%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>118755</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>104619</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>134653</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>36,68%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>222853</t>
+          <t>222562</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>263010</t>
+          <t>261456</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,19%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>42216</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>32407</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>52911</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>13,04%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>16,34%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>36441</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>28458</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>47279</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>27163</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>45807</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>11,72%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>9,15%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>15,21%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>42216</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>33550</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>52875</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>13,04%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>65083</t>
+          <t>66259</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>92040</t>
+          <t>95838</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4618</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>4859</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2156</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>9753</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>10067</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,56%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4493</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3022</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11284</t>
+          <t>11675</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -4814,72 +4814,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3270</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1228</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7511</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>916</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4590</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5594</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>3270</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1192</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>7109</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9564</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>471</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>323795</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>323795</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>323795</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>442</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>310890</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>310890</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>310890</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>323795</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>323795</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>323795</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido estar al aire libre en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el/la menor en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>79786</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>69394</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>90388</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>44,82%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>38,99%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>50,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>84058</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>73070</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>94807</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>71599</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>94631</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>46,66%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>40,56%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>52,62%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>79786</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>67695</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>90508</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>44,82%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>149168</t>
+          <t>148691</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>181266</t>
+          <t>180070</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,28%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>65572</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>55038</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>76829</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>36,84%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>30,92%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>43,16%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>69075</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>59144</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>80521</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>58975</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>80046</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>38,34%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>32,83%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>44,69%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>65572</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>55318</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>76674</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>36,84%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>120043</t>
+          <t>119794</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150765</t>
+          <t>149326</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,69%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28094</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20235</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>36776</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>15,78%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>11,37%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>20,66%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>23509</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17250</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>32448</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>16700</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>30818</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>13,05%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,57%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,01%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28094</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>20895</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>37237</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>15,78%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41625</t>
+          <t>40738</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63733</t>
+          <t>62975</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -5613,72 +5613,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4542</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1751</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10057</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2730</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>762</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6593</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6673</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,66%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4542</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9509</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12315</t>
+          <t>13081</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -5726,107 +5726,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>792</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3993</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4604</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,44%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4390</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4015</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>177994</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>177994</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>177994</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>180163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>180163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>180163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>177994</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>177994</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>177994</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>70730</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>60451</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>81087</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>41,72%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>35,65%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>47,83%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>62763</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>52228</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>73443</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>52096</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>73063</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>38,08%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>31,69%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>44,56%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>70730</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>59100</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>81847</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>41,72%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>118091</t>
+          <t>119037</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149003</t>
+          <t>149674</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,77%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>75119</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>64969</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>86555</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>44,31%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>38,32%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>51,05%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68197</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>57624</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>79705</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>57336</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>79630</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>41,38%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34,96%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>48,36%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>75119</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>63407</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>87105</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>44,31%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128545</t>
+          <t>127308</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>158061</t>
+          <t>158894</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,52%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>20083</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13483</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28437</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>11,85%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>7,95%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>16,77%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>27225</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>19937</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>36543</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>19242</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>35628</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>16,52%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,1%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>22,17%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>20083</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>13464</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>27863</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>11,85%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>35999</t>
+          <t>37259</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>58324</t>
+          <t>58614</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3614</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1392</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8246</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,86%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>4556</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1588</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9325</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9572</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,76%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,66%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3614</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8008</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14015</t>
+          <t>14226</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -6408,72 +6408,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2067</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5771</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,25%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>618</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>5645</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169545</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169545</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169545</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>169545</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>169545</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>169545</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>150515</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>132750</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>164721</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>43,31%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>38,2%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>47,4%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>146820</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>132149</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>162357</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>130353</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>161850</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>42,56%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>38,31%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>47,06%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>150515</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>134576</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>165548</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>43,31%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>274918</t>
+          <t>275639</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>318754</t>
+          <t>321273</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,39%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>140691</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>125511</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>156846</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>40,48%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>36,11%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>45,13%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>137271</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>122242</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>152691</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>122752</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>152332</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>39,79%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>35,44%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>44,26%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>140691</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>126125</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>156471</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>40,48%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>252808</t>
+          <t>257325</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>298504</t>
+          <t>300100</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,34%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>48177</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>38379</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>59931</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>13,86%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>11,04%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>17,24%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>50733</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>41040</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>62274</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>40750</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>62960</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>14,71%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>11,9%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>18,05%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>48177</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>58875</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>13,86%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>84793</t>
+          <t>82967</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>116119</t>
+          <t>114404</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>8156</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4095</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>13903</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>7286</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>3678</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>13233</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>3544</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>12627</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>2,11%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>8156</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>4389</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>14831</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10009</t>
+          <t>9509</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22903</t>
+          <t>22773</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -7090,72 +7090,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>2859</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>786</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>6722</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>7788</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,83%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,23%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>785</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>7073</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>347539</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>347539</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>347539</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>492</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>344970</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>344970</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>344970</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>347539</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>347539</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>347539</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
